--- a/amortization_dashboard/uploads/pricing_data.xlsx
+++ b/amortization_dashboard/uploads/pricing_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\PRICE LIST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C564DE95-6280-436C-8EF9-664FF773DF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005A908A-E96A-4F49-9C54-E5FCA3A22B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" tabRatio="301" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="301" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRICING" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,17 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'FOR PRINT'!$A$1:$X$324</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5702,10 +5713,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="48" x14ac:knownFonts="1">
     <font>
@@ -6271,7 +6282,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6366,12 +6377,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6381,25 +6392,25 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -6439,13 +6450,13 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6466,7 +6477,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6480,10 +6491,10 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6510,7 +6521,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6553,7 +6564,7 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6590,7 +6601,7 @@
     <xf numFmtId="3" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6629,7 +6640,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6650,7 +6661,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6686,7 +6697,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6707,7 +6718,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="25" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6720,7 +6731,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6760,7 +6771,7 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6797,7 +6808,7 @@
     <xf numFmtId="3" fontId="2" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6828,7 +6839,7 @@
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="20" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6846,7 +6857,7 @@
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6904,7 +6915,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6969,7 +6980,7 @@
     <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7038,74 +7049,6 @@
     <xf numFmtId="3" fontId="2" fillId="21" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="15" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7125,6 +7068,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7177,6 +7132,62 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="15" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7517,10 +7528,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="279" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="267"/>
+      <c r="B2" s="279"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -7574,10 +7585,10 @@
       <c r="O4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="268" t="s">
+      <c r="P4" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="Q4" s="269"/>
+      <c r="Q4" s="262"/>
       <c r="R4" s="234">
         <v>6</v>
       </c>
@@ -7585,10 +7596,10 @@
         <v>523</v>
       </c>
       <c r="T4" s="8"/>
-      <c r="U4" s="270" t="s">
+      <c r="U4" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="V4" s="271"/>
+      <c r="V4" s="260"/>
       <c r="W4" s="57" t="s">
         <v>152</v>
       </c>
@@ -7611,30 +7622,30 @@
       <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="273" t="s">
+      <c r="A6" s="281" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="273"/>
-      <c r="C6" s="273"/>
-      <c r="D6" s="273"/>
-      <c r="E6" s="273"/>
-      <c r="F6" s="273"/>
-      <c r="G6" s="273"/>
-      <c r="H6" s="273"/>
-      <c r="I6" s="273"/>
-      <c r="J6" s="273"/>
-      <c r="K6" s="273"/>
-      <c r="L6" s="273"/>
-      <c r="M6" s="273"/>
-      <c r="N6" s="273"/>
-      <c r="O6" s="273"/>
-      <c r="P6" s="273"/>
-      <c r="Q6" s="273"/>
-      <c r="R6" s="273"/>
-      <c r="S6" s="273"/>
-      <c r="T6" s="273"/>
-      <c r="U6" s="273"/>
-      <c r="V6" s="273"/>
+      <c r="B6" s="281"/>
+      <c r="C6" s="281"/>
+      <c r="D6" s="281"/>
+      <c r="E6" s="281"/>
+      <c r="F6" s="281"/>
+      <c r="G6" s="281"/>
+      <c r="H6" s="281"/>
+      <c r="I6" s="281"/>
+      <c r="J6" s="281"/>
+      <c r="K6" s="281"/>
+      <c r="L6" s="281"/>
+      <c r="M6" s="281"/>
+      <c r="N6" s="281"/>
+      <c r="O6" s="281"/>
+      <c r="P6" s="281"/>
+      <c r="Q6" s="281"/>
+      <c r="R6" s="281"/>
+      <c r="S6" s="281"/>
+      <c r="T6" s="281"/>
+      <c r="U6" s="281"/>
+      <c r="V6" s="281"/>
       <c r="W6" s="71"/>
       <c r="X6" s="71"/>
     </row>
@@ -11279,10 +11290,10 @@
       <c r="O56" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="P56" s="275" t="s">
+      <c r="P56" s="253" t="s">
         <v>6</v>
       </c>
-      <c r="Q56" s="276"/>
+      <c r="Q56" s="254"/>
       <c r="R56" s="236">
         <v>6</v>
       </c>
@@ -11290,40 +11301,40 @@
         <v>523</v>
       </c>
       <c r="T56" s="53"/>
-      <c r="U56" s="277" t="s">
+      <c r="U56" s="255" t="s">
         <v>7</v>
       </c>
-      <c r="V56" s="278"/>
+      <c r="V56" s="256"/>
       <c r="W56" s="58" t="s">
         <v>152</v>
       </c>
       <c r="X56" s="58"/>
     </row>
     <row r="57" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="272" t="s">
+      <c r="A57" s="280" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="272"/>
-      <c r="C57" s="272"/>
-      <c r="D57" s="272"/>
-      <c r="E57" s="272"/>
-      <c r="F57" s="272"/>
-      <c r="G57" s="272"/>
-      <c r="H57" s="272"/>
-      <c r="I57" s="272"/>
-      <c r="J57" s="272"/>
-      <c r="K57" s="272"/>
-      <c r="L57" s="272"/>
-      <c r="M57" s="272"/>
-      <c r="N57" s="272"/>
-      <c r="O57" s="272"/>
-      <c r="P57" s="272"/>
-      <c r="Q57" s="272"/>
-      <c r="R57" s="272"/>
-      <c r="S57" s="272"/>
-      <c r="T57" s="272"/>
-      <c r="U57" s="272"/>
-      <c r="V57" s="272"/>
+      <c r="B57" s="280"/>
+      <c r="C57" s="280"/>
+      <c r="D57" s="280"/>
+      <c r="E57" s="280"/>
+      <c r="F57" s="280"/>
+      <c r="G57" s="280"/>
+      <c r="H57" s="280"/>
+      <c r="I57" s="280"/>
+      <c r="J57" s="280"/>
+      <c r="K57" s="280"/>
+      <c r="L57" s="280"/>
+      <c r="M57" s="280"/>
+      <c r="N57" s="280"/>
+      <c r="O57" s="280"/>
+      <c r="P57" s="280"/>
+      <c r="Q57" s="280"/>
+      <c r="R57" s="280"/>
+      <c r="S57" s="280"/>
+      <c r="T57" s="280"/>
+      <c r="U57" s="280"/>
+      <c r="V57" s="280"/>
       <c r="W57" s="71"/>
       <c r="X57" s="71"/>
     </row>
@@ -14066,10 +14077,10 @@
       <c r="O96" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="268" t="s">
+      <c r="P96" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="Q96" s="269"/>
+      <c r="Q96" s="262"/>
       <c r="R96" s="232">
         <v>6</v>
       </c>
@@ -14077,40 +14088,40 @@
         <v>523</v>
       </c>
       <c r="T96" s="8"/>
-      <c r="U96" s="270" t="s">
+      <c r="U96" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="V96" s="271"/>
+      <c r="V96" s="260"/>
       <c r="W96" s="57" t="s">
         <v>152</v>
       </c>
       <c r="X96" s="57"/>
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="281" t="s">
+      <c r="A97" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="B97" s="281"/>
-      <c r="C97" s="281"/>
-      <c r="D97" s="281"/>
-      <c r="E97" s="281"/>
-      <c r="F97" s="281"/>
-      <c r="G97" s="281"/>
-      <c r="H97" s="281"/>
-      <c r="I97" s="281"/>
-      <c r="J97" s="281"/>
-      <c r="K97" s="281"/>
-      <c r="L97" s="281"/>
-      <c r="M97" s="281"/>
-      <c r="N97" s="281"/>
-      <c r="O97" s="281"/>
-      <c r="P97" s="281"/>
-      <c r="Q97" s="281"/>
-      <c r="R97" s="281"/>
-      <c r="S97" s="281"/>
-      <c r="T97" s="281"/>
-      <c r="U97" s="281"/>
-      <c r="V97" s="281"/>
+      <c r="B97" s="263"/>
+      <c r="C97" s="263"/>
+      <c r="D97" s="263"/>
+      <c r="E97" s="263"/>
+      <c r="F97" s="263"/>
+      <c r="G97" s="263"/>
+      <c r="H97" s="263"/>
+      <c r="I97" s="263"/>
+      <c r="J97" s="263"/>
+      <c r="K97" s="263"/>
+      <c r="L97" s="263"/>
+      <c r="M97" s="263"/>
+      <c r="N97" s="263"/>
+      <c r="O97" s="263"/>
+      <c r="P97" s="263"/>
+      <c r="Q97" s="263"/>
+      <c r="R97" s="263"/>
+      <c r="S97" s="263"/>
+      <c r="T97" s="263"/>
+      <c r="U97" s="263"/>
+      <c r="V97" s="263"/>
       <c r="W97" s="71"/>
       <c r="X97" s="71"/>
     </row>
@@ -15013,101 +15024,101 @@
       </c>
     </row>
     <row r="110" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="295">
+      <c r="A110" s="277">
         <v>299500</v>
       </c>
       <c r="B110" s="129" t="s">
         <v>365</v>
       </c>
-      <c r="C110" s="263"/>
-      <c r="D110" s="265" t="str">
+      <c r="C110" s="282"/>
+      <c r="D110" s="284" t="str">
         <f>IF(C110&gt;=1,(K110-C110)*(1+P110*$D$4/100)/$D$4+Q110+R110,"")</f>
         <v/>
       </c>
-      <c r="E110" s="265" t="str">
+      <c r="E110" s="284" t="str">
         <f>IF(C110&gt;=1,(K110-C110)*(1+P110*$E$4/100)/$E$4+Q110+S110,"")</f>
         <v/>
       </c>
-      <c r="F110" s="265" t="str">
+      <c r="F110" s="284" t="str">
         <f>IF(C110&gt;=1,(K110-C110)*(1+$P110*$F$4/100)/$F$4+Q110+S110, "")</f>
         <v/>
       </c>
-      <c r="G110" s="265" t="str">
+      <c r="G110" s="284" t="str">
         <f>IF(C110&gt;=1, (K110-C110)*(1+$P110*$G$4/100)/$G$4+Q110+S110,"")</f>
         <v/>
       </c>
-      <c r="H110" s="252"/>
-      <c r="I110" s="252"/>
+      <c r="H110" s="292"/>
+      <c r="I110" s="292"/>
       <c r="J110" s="121"/>
-      <c r="K110" s="259">
+      <c r="K110" s="288">
         <v>301921</v>
       </c>
-      <c r="L110" s="259">
+      <c r="L110" s="288">
         <v>299500</v>
       </c>
-      <c r="M110" s="261">
+      <c r="M110" s="290">
         <f>300307+1200</f>
         <v>301507</v>
       </c>
-      <c r="N110" s="261">
+      <c r="N110" s="290">
         <f>301114+1200</f>
         <v>302314</v>
       </c>
-      <c r="O110" s="261">
+      <c r="O110" s="290">
         <f>301921+1100</f>
         <v>303021</v>
       </c>
-      <c r="P110" s="254">
+      <c r="P110" s="294">
         <v>2.17</v>
       </c>
       <c r="Q110" s="124"/>
-      <c r="R110" s="256">
+      <c r="R110" s="296">
         <v>250</v>
       </c>
-      <c r="S110" s="256">
+      <c r="S110" s="296">
         <v>125</v>
       </c>
       <c r="T110" s="121"/>
-      <c r="U110" s="255">
+      <c r="U110" s="295">
         <v>350</v>
       </c>
-      <c r="V110" s="255">
+      <c r="V110" s="295">
         <v>100</v>
       </c>
-      <c r="W110" s="257" t="s">
+      <c r="W110" s="286" t="s">
         <v>467</v>
       </c>
-      <c r="X110" s="258" t="s">
+      <c r="X110" s="287" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="296"/>
+      <c r="A111" s="278"/>
       <c r="B111" s="129" t="s">
         <v>491</v>
       </c>
-      <c r="C111" s="264"/>
-      <c r="D111" s="266"/>
-      <c r="E111" s="266"/>
-      <c r="F111" s="266"/>
-      <c r="G111" s="266"/>
-      <c r="H111" s="253"/>
-      <c r="I111" s="253"/>
+      <c r="C111" s="283"/>
+      <c r="D111" s="285"/>
+      <c r="E111" s="285"/>
+      <c r="F111" s="285"/>
+      <c r="G111" s="285"/>
+      <c r="H111" s="293"/>
+      <c r="I111" s="293"/>
       <c r="J111" s="121"/>
-      <c r="K111" s="260"/>
-      <c r="L111" s="260"/>
-      <c r="M111" s="262"/>
-      <c r="N111" s="262"/>
-      <c r="O111" s="262"/>
-      <c r="P111" s="254"/>
+      <c r="K111" s="289"/>
+      <c r="L111" s="289"/>
+      <c r="M111" s="291"/>
+      <c r="N111" s="291"/>
+      <c r="O111" s="291"/>
+      <c r="P111" s="294"/>
       <c r="Q111" s="124"/>
-      <c r="R111" s="256"/>
-      <c r="S111" s="256"/>
+      <c r="R111" s="296"/>
+      <c r="S111" s="296"/>
       <c r="T111" s="121"/>
-      <c r="U111" s="255"/>
-      <c r="V111" s="255"/>
-      <c r="W111" s="257"/>
-      <c r="X111" s="258"/>
+      <c r="U111" s="295"/>
+      <c r="V111" s="295"/>
+      <c r="W111" s="286"/>
+      <c r="X111" s="287"/>
     </row>
     <row r="112" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="245">
@@ -21311,32 +21322,32 @@
       <c r="B195" s="198" t="s">
         <v>206</v>
       </c>
-      <c r="C195" s="282" t="s">
+      <c r="C195" s="264" t="s">
         <v>281</v>
       </c>
-      <c r="D195" s="283"/>
-      <c r="E195" s="283"/>
-      <c r="F195" s="283"/>
-      <c r="G195" s="283"/>
-      <c r="H195" s="283"/>
-      <c r="I195" s="283"/>
+      <c r="D195" s="265"/>
+      <c r="E195" s="265"/>
+      <c r="F195" s="265"/>
+      <c r="G195" s="265"/>
+      <c r="H195" s="265"/>
+      <c r="I195" s="265"/>
       <c r="J195" s="114"/>
-      <c r="K195" s="284" t="s">
+      <c r="K195" s="266" t="s">
         <v>211</v>
       </c>
-      <c r="L195" s="285"/>
-      <c r="M195" s="285"/>
-      <c r="N195" s="285"/>
-      <c r="O195" s="285"/>
-      <c r="P195" s="285"/>
-      <c r="Q195" s="285"/>
-      <c r="R195" s="285"/>
-      <c r="S195" s="285"/>
-      <c r="T195" s="285"/>
-      <c r="U195" s="285"/>
-      <c r="V195" s="285"/>
-      <c r="W195" s="285"/>
-      <c r="X195" s="285"/>
+      <c r="L195" s="267"/>
+      <c r="M195" s="267"/>
+      <c r="N195" s="267"/>
+      <c r="O195" s="267"/>
+      <c r="P195" s="267"/>
+      <c r="Q195" s="267"/>
+      <c r="R195" s="267"/>
+      <c r="S195" s="267"/>
+      <c r="T195" s="267"/>
+      <c r="U195" s="267"/>
+      <c r="V195" s="267"/>
+      <c r="W195" s="267"/>
+      <c r="X195" s="267"/>
     </row>
     <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196" s="113">
@@ -21787,32 +21798,32 @@
       <c r="B202" s="220" t="s">
         <v>311</v>
       </c>
-      <c r="C202" s="286" t="s">
+      <c r="C202" s="268" t="s">
         <v>312</v>
       </c>
-      <c r="D202" s="287"/>
-      <c r="E202" s="287"/>
-      <c r="F202" s="287"/>
-      <c r="G202" s="287"/>
-      <c r="H202" s="287"/>
-      <c r="I202" s="287"/>
+      <c r="D202" s="269"/>
+      <c r="E202" s="269"/>
+      <c r="F202" s="269"/>
+      <c r="G202" s="269"/>
+      <c r="H202" s="269"/>
+      <c r="I202" s="269"/>
       <c r="J202" s="219"/>
-      <c r="K202" s="288" t="s">
+      <c r="K202" s="270" t="s">
         <v>311</v>
       </c>
-      <c r="L202" s="289"/>
-      <c r="M202" s="289"/>
-      <c r="N202" s="289"/>
-      <c r="O202" s="289"/>
-      <c r="P202" s="289"/>
-      <c r="Q202" s="289"/>
-      <c r="R202" s="289"/>
-      <c r="S202" s="289"/>
-      <c r="T202" s="289"/>
-      <c r="U202" s="289"/>
-      <c r="V202" s="289"/>
-      <c r="W202" s="289"/>
-      <c r="X202" s="290"/>
+      <c r="L202" s="271"/>
+      <c r="M202" s="271"/>
+      <c r="N202" s="271"/>
+      <c r="O202" s="271"/>
+      <c r="P202" s="271"/>
+      <c r="Q202" s="271"/>
+      <c r="R202" s="271"/>
+      <c r="S202" s="271"/>
+      <c r="T202" s="271"/>
+      <c r="U202" s="271"/>
+      <c r="V202" s="271"/>
+      <c r="W202" s="271"/>
+      <c r="X202" s="272"/>
     </row>
     <row r="203" spans="1:24" s="128" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="113">
@@ -22275,32 +22286,32 @@
       <c r="B209" s="222" t="s">
         <v>348</v>
       </c>
-      <c r="C209" s="286" t="s">
+      <c r="C209" s="268" t="s">
         <v>349</v>
       </c>
-      <c r="D209" s="287"/>
-      <c r="E209" s="287"/>
-      <c r="F209" s="287"/>
-      <c r="G209" s="287"/>
-      <c r="H209" s="287"/>
-      <c r="I209" s="287"/>
+      <c r="D209" s="269"/>
+      <c r="E209" s="269"/>
+      <c r="F209" s="269"/>
+      <c r="G209" s="269"/>
+      <c r="H209" s="269"/>
+      <c r="I209" s="269"/>
       <c r="J209" s="219"/>
-      <c r="K209" s="292" t="s">
+      <c r="K209" s="274" t="s">
         <v>348</v>
       </c>
-      <c r="L209" s="293"/>
-      <c r="M209" s="293"/>
-      <c r="N209" s="293"/>
-      <c r="O209" s="293"/>
-      <c r="P209" s="293"/>
-      <c r="Q209" s="293"/>
-      <c r="R209" s="293"/>
-      <c r="S209" s="293"/>
-      <c r="T209" s="293"/>
-      <c r="U209" s="293"/>
-      <c r="V209" s="293"/>
-      <c r="W209" s="293"/>
-      <c r="X209" s="294"/>
+      <c r="L209" s="275"/>
+      <c r="M209" s="275"/>
+      <c r="N209" s="275"/>
+      <c r="O209" s="275"/>
+      <c r="P209" s="275"/>
+      <c r="Q209" s="275"/>
+      <c r="R209" s="275"/>
+      <c r="S209" s="275"/>
+      <c r="T209" s="275"/>
+      <c r="U209" s="275"/>
+      <c r="V209" s="275"/>
+      <c r="W209" s="275"/>
+      <c r="X209" s="276"/>
     </row>
     <row r="210" spans="1:24" s="128" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="113">
@@ -22461,30 +22472,30 @@
       </c>
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A212" s="291"/>
-      <c r="B212" s="291"/>
-      <c r="C212" s="291"/>
-      <c r="D212" s="291"/>
-      <c r="E212" s="291"/>
-      <c r="F212" s="291"/>
-      <c r="G212" s="291"/>
-      <c r="H212" s="291"/>
-      <c r="I212" s="291"/>
-      <c r="J212" s="291"/>
-      <c r="K212" s="291"/>
-      <c r="L212" s="291"/>
-      <c r="M212" s="291"/>
-      <c r="N212" s="291"/>
-      <c r="O212" s="291"/>
-      <c r="P212" s="291"/>
-      <c r="Q212" s="291"/>
-      <c r="R212" s="291"/>
-      <c r="S212" s="291"/>
-      <c r="T212" s="291"/>
-      <c r="U212" s="291"/>
-      <c r="V212" s="291"/>
-      <c r="W212" s="291"/>
-      <c r="X212" s="291"/>
+      <c r="A212" s="273"/>
+      <c r="B212" s="273"/>
+      <c r="C212" s="273"/>
+      <c r="D212" s="273"/>
+      <c r="E212" s="273"/>
+      <c r="F212" s="273"/>
+      <c r="G212" s="273"/>
+      <c r="H212" s="273"/>
+      <c r="I212" s="273"/>
+      <c r="J212" s="273"/>
+      <c r="K212" s="273"/>
+      <c r="L212" s="273"/>
+      <c r="M212" s="273"/>
+      <c r="N212" s="273"/>
+      <c r="O212" s="273"/>
+      <c r="P212" s="273"/>
+      <c r="Q212" s="273"/>
+      <c r="R212" s="273"/>
+      <c r="S212" s="273"/>
+      <c r="T212" s="273"/>
+      <c r="U212" s="273"/>
+      <c r="V212" s="273"/>
+      <c r="W212" s="273"/>
+      <c r="X212" s="273"/>
     </row>
     <row r="213" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="61" t="s">
@@ -22529,10 +22540,10 @@
       <c r="O213" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="P213" s="279" t="s">
+      <c r="P213" s="257" t="s">
         <v>6</v>
       </c>
-      <c r="Q213" s="280"/>
+      <c r="Q213" s="258"/>
       <c r="R213" s="239">
         <v>6</v>
       </c>
@@ -22540,40 +22551,40 @@
         <v>523</v>
       </c>
       <c r="T213" s="56"/>
-      <c r="U213" s="270" t="s">
+      <c r="U213" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="V213" s="271"/>
+      <c r="V213" s="260"/>
       <c r="W213" s="59" t="s">
         <v>152</v>
       </c>
       <c r="X213" s="59"/>
     </row>
     <row r="214" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="274" t="s">
+      <c r="A214" s="252" t="s">
         <v>22</v>
       </c>
-      <c r="B214" s="274"/>
-      <c r="C214" s="274"/>
-      <c r="D214" s="274"/>
-      <c r="E214" s="274"/>
-      <c r="F214" s="274"/>
-      <c r="G214" s="274"/>
-      <c r="H214" s="274"/>
-      <c r="I214" s="274"/>
-      <c r="J214" s="274"/>
-      <c r="K214" s="274"/>
-      <c r="L214" s="274"/>
-      <c r="M214" s="274"/>
-      <c r="N214" s="274"/>
-      <c r="O214" s="274"/>
-      <c r="P214" s="274"/>
-      <c r="Q214" s="274"/>
-      <c r="R214" s="274"/>
-      <c r="S214" s="274"/>
-      <c r="T214" s="274"/>
-      <c r="U214" s="274"/>
-      <c r="V214" s="274"/>
+      <c r="B214" s="252"/>
+      <c r="C214" s="252"/>
+      <c r="D214" s="252"/>
+      <c r="E214" s="252"/>
+      <c r="F214" s="252"/>
+      <c r="G214" s="252"/>
+      <c r="H214" s="252"/>
+      <c r="I214" s="252"/>
+      <c r="J214" s="252"/>
+      <c r="K214" s="252"/>
+      <c r="L214" s="252"/>
+      <c r="M214" s="252"/>
+      <c r="N214" s="252"/>
+      <c r="O214" s="252"/>
+      <c r="P214" s="252"/>
+      <c r="Q214" s="252"/>
+      <c r="R214" s="252"/>
+      <c r="S214" s="252"/>
+      <c r="T214" s="252"/>
+      <c r="U214" s="252"/>
+      <c r="V214" s="252"/>
       <c r="W214" s="71"/>
       <c r="X214" s="71"/>
     </row>
@@ -30390,6 +30401,30 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Sk06WJo0GhSUyXaRtk3ws5dtrOTisueabBrT2tDtVUCtPQ1eB8CnjrHIkz2Wx/9++Dq+w1AdudD1H8oJHx5sJQ==" saltValue="DuhdztxXn/2cfzMc7SFabQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="40">
+    <mergeCell ref="H110:H111"/>
+    <mergeCell ref="I110:I111"/>
+    <mergeCell ref="P110:P111"/>
+    <mergeCell ref="U110:U111"/>
+    <mergeCell ref="V110:V111"/>
+    <mergeCell ref="R110:R111"/>
+    <mergeCell ref="S110:S111"/>
+    <mergeCell ref="W110:W111"/>
+    <mergeCell ref="X110:X111"/>
+    <mergeCell ref="K110:K111"/>
+    <mergeCell ref="L110:L111"/>
+    <mergeCell ref="M110:M111"/>
+    <mergeCell ref="N110:N111"/>
+    <mergeCell ref="O110:O111"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="E110:E111"/>
+    <mergeCell ref="F110:F111"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="A57:V57"/>
+    <mergeCell ref="A6:V6"/>
     <mergeCell ref="A214:V214"/>
     <mergeCell ref="P56:Q56"/>
     <mergeCell ref="U56:V56"/>
@@ -30406,30 +30441,6 @@
     <mergeCell ref="C209:I209"/>
     <mergeCell ref="K209:X209"/>
     <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="A57:V57"/>
-    <mergeCell ref="A6:V6"/>
-    <mergeCell ref="C110:C111"/>
-    <mergeCell ref="D110:D111"/>
-    <mergeCell ref="E110:E111"/>
-    <mergeCell ref="F110:F111"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="W110:W111"/>
-    <mergeCell ref="X110:X111"/>
-    <mergeCell ref="K110:K111"/>
-    <mergeCell ref="L110:L111"/>
-    <mergeCell ref="M110:M111"/>
-    <mergeCell ref="N110:N111"/>
-    <mergeCell ref="O110:O111"/>
-    <mergeCell ref="H110:H111"/>
-    <mergeCell ref="I110:I111"/>
-    <mergeCell ref="P110:P111"/>
-    <mergeCell ref="U110:U111"/>
-    <mergeCell ref="V110:V111"/>
-    <mergeCell ref="R110:R111"/>
-    <mergeCell ref="S110:S111"/>
   </mergeCells>
   <phoneticPr fontId="43" type="noConversion"/>
   <conditionalFormatting sqref="C27">
@@ -30526,10 +30537,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="267" t="s">
+      <c r="A2" s="279" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="267"/>
+      <c r="B2" s="279"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -30583,10 +30594,10 @@
       <c r="O4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="268" t="s">
+      <c r="P4" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="Q4" s="269"/>
+      <c r="Q4" s="262"/>
       <c r="R4" s="234">
         <v>6</v>
       </c>
@@ -30594,10 +30605,10 @@
         <v>523</v>
       </c>
       <c r="T4" s="8"/>
-      <c r="U4" s="270" t="s">
+      <c r="U4" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="V4" s="271"/>
+      <c r="V4" s="260"/>
       <c r="W4" s="57" t="s">
         <v>152</v>
       </c>
@@ -30620,30 +30631,30 @@
       <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="273" t="s">
+      <c r="A6" s="281" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="273"/>
-      <c r="C6" s="273"/>
-      <c r="D6" s="273"/>
-      <c r="E6" s="273"/>
-      <c r="F6" s="273"/>
-      <c r="G6" s="273"/>
-      <c r="H6" s="273"/>
-      <c r="I6" s="273"/>
-      <c r="J6" s="273"/>
-      <c r="K6" s="273"/>
-      <c r="L6" s="273"/>
-      <c r="M6" s="273"/>
-      <c r="N6" s="273"/>
-      <c r="O6" s="273"/>
-      <c r="P6" s="273"/>
-      <c r="Q6" s="273"/>
-      <c r="R6" s="273"/>
-      <c r="S6" s="273"/>
-      <c r="T6" s="273"/>
-      <c r="U6" s="273"/>
-      <c r="V6" s="273"/>
+      <c r="B6" s="281"/>
+      <c r="C6" s="281"/>
+      <c r="D6" s="281"/>
+      <c r="E6" s="281"/>
+      <c r="F6" s="281"/>
+      <c r="G6" s="281"/>
+      <c r="H6" s="281"/>
+      <c r="I6" s="281"/>
+      <c r="J6" s="281"/>
+      <c r="K6" s="281"/>
+      <c r="L6" s="281"/>
+      <c r="M6" s="281"/>
+      <c r="N6" s="281"/>
+      <c r="O6" s="281"/>
+      <c r="P6" s="281"/>
+      <c r="Q6" s="281"/>
+      <c r="R6" s="281"/>
+      <c r="S6" s="281"/>
+      <c r="T6" s="281"/>
+      <c r="U6" s="281"/>
+      <c r="V6" s="281"/>
       <c r="W6" s="71"/>
       <c r="X6" s="71"/>
     </row>
@@ -34288,10 +34299,10 @@
       <c r="O56" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="P56" s="275" t="s">
+      <c r="P56" s="253" t="s">
         <v>6</v>
       </c>
-      <c r="Q56" s="276"/>
+      <c r="Q56" s="254"/>
       <c r="R56" s="236">
         <v>6</v>
       </c>
@@ -34299,40 +34310,40 @@
         <v>523</v>
       </c>
       <c r="T56" s="53"/>
-      <c r="U56" s="277" t="s">
+      <c r="U56" s="255" t="s">
         <v>7</v>
       </c>
-      <c r="V56" s="278"/>
+      <c r="V56" s="256"/>
       <c r="W56" s="58" t="s">
         <v>152</v>
       </c>
       <c r="X56" s="58"/>
     </row>
     <row r="57" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="272" t="s">
+      <c r="A57" s="280" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="272"/>
-      <c r="C57" s="272"/>
-      <c r="D57" s="272"/>
-      <c r="E57" s="272"/>
-      <c r="F57" s="272"/>
-      <c r="G57" s="272"/>
-      <c r="H57" s="272"/>
-      <c r="I57" s="272"/>
-      <c r="J57" s="272"/>
-      <c r="K57" s="272"/>
-      <c r="L57" s="272"/>
-      <c r="M57" s="272"/>
-      <c r="N57" s="272"/>
-      <c r="O57" s="272"/>
-      <c r="P57" s="272"/>
-      <c r="Q57" s="272"/>
-      <c r="R57" s="272"/>
-      <c r="S57" s="272"/>
-      <c r="T57" s="272"/>
-      <c r="U57" s="272"/>
-      <c r="V57" s="272"/>
+      <c r="B57" s="280"/>
+      <c r="C57" s="280"/>
+      <c r="D57" s="280"/>
+      <c r="E57" s="280"/>
+      <c r="F57" s="280"/>
+      <c r="G57" s="280"/>
+      <c r="H57" s="280"/>
+      <c r="I57" s="280"/>
+      <c r="J57" s="280"/>
+      <c r="K57" s="280"/>
+      <c r="L57" s="280"/>
+      <c r="M57" s="280"/>
+      <c r="N57" s="280"/>
+      <c r="O57" s="280"/>
+      <c r="P57" s="280"/>
+      <c r="Q57" s="280"/>
+      <c r="R57" s="280"/>
+      <c r="S57" s="280"/>
+      <c r="T57" s="280"/>
+      <c r="U57" s="280"/>
+      <c r="V57" s="280"/>
       <c r="W57" s="71"/>
       <c r="X57" s="71"/>
     </row>
@@ -37075,10 +37086,10 @@
       <c r="O96" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="268" t="s">
+      <c r="P96" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="Q96" s="269"/>
+      <c r="Q96" s="262"/>
       <c r="R96" s="232">
         <v>6</v>
       </c>
@@ -37086,40 +37097,40 @@
         <v>523</v>
       </c>
       <c r="T96" s="8"/>
-      <c r="U96" s="270" t="s">
+      <c r="U96" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="V96" s="271"/>
+      <c r="V96" s="260"/>
       <c r="W96" s="57" t="s">
         <v>152</v>
       </c>
       <c r="X96" s="57"/>
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="281" t="s">
+      <c r="A97" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="B97" s="281"/>
-      <c r="C97" s="281"/>
-      <c r="D97" s="281"/>
-      <c r="E97" s="281"/>
-      <c r="F97" s="281"/>
-      <c r="G97" s="281"/>
-      <c r="H97" s="281"/>
-      <c r="I97" s="281"/>
-      <c r="J97" s="281"/>
-      <c r="K97" s="281"/>
-      <c r="L97" s="281"/>
-      <c r="M97" s="281"/>
-      <c r="N97" s="281"/>
-      <c r="O97" s="281"/>
-      <c r="P97" s="281"/>
-      <c r="Q97" s="281"/>
-      <c r="R97" s="281"/>
-      <c r="S97" s="281"/>
-      <c r="T97" s="281"/>
-      <c r="U97" s="281"/>
-      <c r="V97" s="281"/>
+      <c r="B97" s="263"/>
+      <c r="C97" s="263"/>
+      <c r="D97" s="263"/>
+      <c r="E97" s="263"/>
+      <c r="F97" s="263"/>
+      <c r="G97" s="263"/>
+      <c r="H97" s="263"/>
+      <c r="I97" s="263"/>
+      <c r="J97" s="263"/>
+      <c r="K97" s="263"/>
+      <c r="L97" s="263"/>
+      <c r="M97" s="263"/>
+      <c r="N97" s="263"/>
+      <c r="O97" s="263"/>
+      <c r="P97" s="263"/>
+      <c r="Q97" s="263"/>
+      <c r="R97" s="263"/>
+      <c r="S97" s="263"/>
+      <c r="T97" s="263"/>
+      <c r="U97" s="263"/>
+      <c r="V97" s="263"/>
       <c r="W97" s="71"/>
       <c r="X97" s="71"/>
     </row>
@@ -38022,101 +38033,101 @@
       </c>
     </row>
     <row r="110" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="295">
+      <c r="A110" s="277">
         <v>299500</v>
       </c>
       <c r="B110" s="129" t="s">
         <v>365</v>
       </c>
-      <c r="C110" s="263"/>
-      <c r="D110" s="265" t="str">
+      <c r="C110" s="282"/>
+      <c r="D110" s="284" t="str">
         <f>IF(C110&gt;=1,(K110-C110)*(1+P110*$D$4/100)/$D$4+Q110+R110,"")</f>
         <v/>
       </c>
-      <c r="E110" s="265" t="str">
+      <c r="E110" s="284" t="str">
         <f>IF(C110&gt;=1,(K110-C110)*(1+P110*$E$4/100)/$E$4+Q110+S110,"")</f>
         <v/>
       </c>
-      <c r="F110" s="265" t="str">
+      <c r="F110" s="284" t="str">
         <f>IF(C110&gt;=1,(K110-C110)*(1+$P110*$F$4/100)/$F$4+Q110+S110, "")</f>
         <v/>
       </c>
-      <c r="G110" s="265" t="str">
+      <c r="G110" s="284" t="str">
         <f>IF(C110&gt;=1, (K110-C110)*(1+$P110*$G$4/100)/$G$4+Q110+S110,"")</f>
         <v/>
       </c>
-      <c r="H110" s="252"/>
-      <c r="I110" s="252"/>
+      <c r="H110" s="292"/>
+      <c r="I110" s="292"/>
       <c r="J110" s="121"/>
-      <c r="K110" s="259">
+      <c r="K110" s="288">
         <v>301921</v>
       </c>
-      <c r="L110" s="259">
+      <c r="L110" s="288">
         <v>299500</v>
       </c>
-      <c r="M110" s="261">
+      <c r="M110" s="290">
         <f>300307+1200</f>
         <v>301507</v>
       </c>
-      <c r="N110" s="261">
+      <c r="N110" s="290">
         <f>301114+1200</f>
         <v>302314</v>
       </c>
-      <c r="O110" s="261">
+      <c r="O110" s="290">
         <f>301921+1100</f>
         <v>303021</v>
       </c>
-      <c r="P110" s="254">
+      <c r="P110" s="294">
         <v>2.17</v>
       </c>
       <c r="Q110" s="124"/>
-      <c r="R110" s="256">
+      <c r="R110" s="296">
         <v>250</v>
       </c>
-      <c r="S110" s="256">
+      <c r="S110" s="296">
         <v>125</v>
       </c>
       <c r="T110" s="121"/>
-      <c r="U110" s="255">
+      <c r="U110" s="295">
         <v>350</v>
       </c>
-      <c r="V110" s="255">
+      <c r="V110" s="295">
         <v>100</v>
       </c>
-      <c r="W110" s="257" t="s">
+      <c r="W110" s="286" t="s">
         <v>467</v>
       </c>
-      <c r="X110" s="258" t="s">
+      <c r="X110" s="287" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="296"/>
+      <c r="A111" s="278"/>
       <c r="B111" s="129" t="s">
         <v>491</v>
       </c>
-      <c r="C111" s="264"/>
-      <c r="D111" s="266"/>
-      <c r="E111" s="266"/>
-      <c r="F111" s="266"/>
-      <c r="G111" s="266"/>
-      <c r="H111" s="253"/>
-      <c r="I111" s="253"/>
+      <c r="C111" s="283"/>
+      <c r="D111" s="285"/>
+      <c r="E111" s="285"/>
+      <c r="F111" s="285"/>
+      <c r="G111" s="285"/>
+      <c r="H111" s="293"/>
+      <c r="I111" s="293"/>
       <c r="J111" s="121"/>
-      <c r="K111" s="260"/>
-      <c r="L111" s="260"/>
-      <c r="M111" s="262"/>
-      <c r="N111" s="262"/>
-      <c r="O111" s="262"/>
-      <c r="P111" s="254"/>
+      <c r="K111" s="289"/>
+      <c r="L111" s="289"/>
+      <c r="M111" s="291"/>
+      <c r="N111" s="291"/>
+      <c r="O111" s="291"/>
+      <c r="P111" s="294"/>
       <c r="Q111" s="124"/>
-      <c r="R111" s="256"/>
-      <c r="S111" s="256"/>
+      <c r="R111" s="296"/>
+      <c r="S111" s="296"/>
       <c r="T111" s="121"/>
-      <c r="U111" s="255"/>
-      <c r="V111" s="255"/>
-      <c r="W111" s="257"/>
-      <c r="X111" s="258"/>
+      <c r="U111" s="295"/>
+      <c r="V111" s="295"/>
+      <c r="W111" s="286"/>
+      <c r="X111" s="287"/>
     </row>
     <row r="112" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="245">
@@ -44320,32 +44331,32 @@
       <c r="B195" s="198" t="s">
         <v>206</v>
       </c>
-      <c r="C195" s="282" t="s">
+      <c r="C195" s="264" t="s">
         <v>281</v>
       </c>
-      <c r="D195" s="283"/>
-      <c r="E195" s="283"/>
-      <c r="F195" s="283"/>
-      <c r="G195" s="283"/>
-      <c r="H195" s="283"/>
-      <c r="I195" s="283"/>
+      <c r="D195" s="265"/>
+      <c r="E195" s="265"/>
+      <c r="F195" s="265"/>
+      <c r="G195" s="265"/>
+      <c r="H195" s="265"/>
+      <c r="I195" s="265"/>
       <c r="J195" s="114"/>
-      <c r="K195" s="284" t="s">
+      <c r="K195" s="266" t="s">
         <v>211</v>
       </c>
-      <c r="L195" s="285"/>
-      <c r="M195" s="285"/>
-      <c r="N195" s="285"/>
-      <c r="O195" s="285"/>
-      <c r="P195" s="285"/>
-      <c r="Q195" s="285"/>
-      <c r="R195" s="285"/>
-      <c r="S195" s="285"/>
-      <c r="T195" s="285"/>
-      <c r="U195" s="285"/>
-      <c r="V195" s="285"/>
-      <c r="W195" s="285"/>
-      <c r="X195" s="285"/>
+      <c r="L195" s="267"/>
+      <c r="M195" s="267"/>
+      <c r="N195" s="267"/>
+      <c r="O195" s="267"/>
+      <c r="P195" s="267"/>
+      <c r="Q195" s="267"/>
+      <c r="R195" s="267"/>
+      <c r="S195" s="267"/>
+      <c r="T195" s="267"/>
+      <c r="U195" s="267"/>
+      <c r="V195" s="267"/>
+      <c r="W195" s="267"/>
+      <c r="X195" s="267"/>
     </row>
     <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196" s="113">
@@ -44796,32 +44807,32 @@
       <c r="B202" s="220" t="s">
         <v>311</v>
       </c>
-      <c r="C202" s="286" t="s">
+      <c r="C202" s="268" t="s">
         <v>312</v>
       </c>
-      <c r="D202" s="287"/>
-      <c r="E202" s="287"/>
-      <c r="F202" s="287"/>
-      <c r="G202" s="287"/>
-      <c r="H202" s="287"/>
-      <c r="I202" s="287"/>
+      <c r="D202" s="269"/>
+      <c r="E202" s="269"/>
+      <c r="F202" s="269"/>
+      <c r="G202" s="269"/>
+      <c r="H202" s="269"/>
+      <c r="I202" s="269"/>
       <c r="J202" s="219"/>
-      <c r="K202" s="288" t="s">
+      <c r="K202" s="270" t="s">
         <v>311</v>
       </c>
-      <c r="L202" s="289"/>
-      <c r="M202" s="289"/>
-      <c r="N202" s="289"/>
-      <c r="O202" s="289"/>
-      <c r="P202" s="289"/>
-      <c r="Q202" s="289"/>
-      <c r="R202" s="289"/>
-      <c r="S202" s="289"/>
-      <c r="T202" s="289"/>
-      <c r="U202" s="289"/>
-      <c r="V202" s="289"/>
-      <c r="W202" s="289"/>
-      <c r="X202" s="290"/>
+      <c r="L202" s="271"/>
+      <c r="M202" s="271"/>
+      <c r="N202" s="271"/>
+      <c r="O202" s="271"/>
+      <c r="P202" s="271"/>
+      <c r="Q202" s="271"/>
+      <c r="R202" s="271"/>
+      <c r="S202" s="271"/>
+      <c r="T202" s="271"/>
+      <c r="U202" s="271"/>
+      <c r="V202" s="271"/>
+      <c r="W202" s="271"/>
+      <c r="X202" s="272"/>
     </row>
     <row r="203" spans="1:24" s="128" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="113">
@@ -45284,32 +45295,32 @@
       <c r="B209" s="222" t="s">
         <v>348</v>
       </c>
-      <c r="C209" s="286" t="s">
+      <c r="C209" s="268" t="s">
         <v>349</v>
       </c>
-      <c r="D209" s="287"/>
-      <c r="E209" s="287"/>
-      <c r="F209" s="287"/>
-      <c r="G209" s="287"/>
-      <c r="H209" s="287"/>
-      <c r="I209" s="287"/>
+      <c r="D209" s="269"/>
+      <c r="E209" s="269"/>
+      <c r="F209" s="269"/>
+      <c r="G209" s="269"/>
+      <c r="H209" s="269"/>
+      <c r="I209" s="269"/>
       <c r="J209" s="219"/>
-      <c r="K209" s="292" t="s">
+      <c r="K209" s="274" t="s">
         <v>348</v>
       </c>
-      <c r="L209" s="293"/>
-      <c r="M209" s="293"/>
-      <c r="N209" s="293"/>
-      <c r="O209" s="293"/>
-      <c r="P209" s="293"/>
-      <c r="Q209" s="293"/>
-      <c r="R209" s="293"/>
-      <c r="S209" s="293"/>
-      <c r="T209" s="293"/>
-      <c r="U209" s="293"/>
-      <c r="V209" s="293"/>
-      <c r="W209" s="293"/>
-      <c r="X209" s="294"/>
+      <c r="L209" s="275"/>
+      <c r="M209" s="275"/>
+      <c r="N209" s="275"/>
+      <c r="O209" s="275"/>
+      <c r="P209" s="275"/>
+      <c r="Q209" s="275"/>
+      <c r="R209" s="275"/>
+      <c r="S209" s="275"/>
+      <c r="T209" s="275"/>
+      <c r="U209" s="275"/>
+      <c r="V209" s="275"/>
+      <c r="W209" s="275"/>
+      <c r="X209" s="276"/>
     </row>
     <row r="210" spans="1:24" s="128" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="113">
@@ -45470,30 +45481,30 @@
       </c>
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A212" s="291"/>
-      <c r="B212" s="291"/>
-      <c r="C212" s="291"/>
-      <c r="D212" s="291"/>
-      <c r="E212" s="291"/>
-      <c r="F212" s="291"/>
-      <c r="G212" s="291"/>
-      <c r="H212" s="291"/>
-      <c r="I212" s="291"/>
-      <c r="J212" s="291"/>
-      <c r="K212" s="291"/>
-      <c r="L212" s="291"/>
-      <c r="M212" s="291"/>
-      <c r="N212" s="291"/>
-      <c r="O212" s="291"/>
-      <c r="P212" s="291"/>
-      <c r="Q212" s="291"/>
-      <c r="R212" s="291"/>
-      <c r="S212" s="291"/>
-      <c r="T212" s="291"/>
-      <c r="U212" s="291"/>
-      <c r="V212" s="291"/>
-      <c r="W212" s="291"/>
-      <c r="X212" s="291"/>
+      <c r="A212" s="273"/>
+      <c r="B212" s="273"/>
+      <c r="C212" s="273"/>
+      <c r="D212" s="273"/>
+      <c r="E212" s="273"/>
+      <c r="F212" s="273"/>
+      <c r="G212" s="273"/>
+      <c r="H212" s="273"/>
+      <c r="I212" s="273"/>
+      <c r="J212" s="273"/>
+      <c r="K212" s="273"/>
+      <c r="L212" s="273"/>
+      <c r="M212" s="273"/>
+      <c r="N212" s="273"/>
+      <c r="O212" s="273"/>
+      <c r="P212" s="273"/>
+      <c r="Q212" s="273"/>
+      <c r="R212" s="273"/>
+      <c r="S212" s="273"/>
+      <c r="T212" s="273"/>
+      <c r="U212" s="273"/>
+      <c r="V212" s="273"/>
+      <c r="W212" s="273"/>
+      <c r="X212" s="273"/>
     </row>
     <row r="213" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="61" t="s">
@@ -45538,10 +45549,10 @@
       <c r="O213" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="P213" s="279" t="s">
+      <c r="P213" s="257" t="s">
         <v>6</v>
       </c>
-      <c r="Q213" s="280"/>
+      <c r="Q213" s="258"/>
       <c r="R213" s="239">
         <v>6</v>
       </c>
@@ -45549,40 +45560,40 @@
         <v>523</v>
       </c>
       <c r="T213" s="56"/>
-      <c r="U213" s="270" t="s">
+      <c r="U213" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="V213" s="271"/>
+      <c r="V213" s="260"/>
       <c r="W213" s="59" t="s">
         <v>152</v>
       </c>
       <c r="X213" s="59"/>
     </row>
     <row r="214" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="274" t="s">
+      <c r="A214" s="252" t="s">
         <v>22</v>
       </c>
-      <c r="B214" s="274"/>
-      <c r="C214" s="274"/>
-      <c r="D214" s="274"/>
-      <c r="E214" s="274"/>
-      <c r="F214" s="274"/>
-      <c r="G214" s="274"/>
-      <c r="H214" s="274"/>
-      <c r="I214" s="274"/>
-      <c r="J214" s="274"/>
-      <c r="K214" s="274"/>
-      <c r="L214" s="274"/>
-      <c r="M214" s="274"/>
-      <c r="N214" s="274"/>
-      <c r="O214" s="274"/>
-      <c r="P214" s="274"/>
-      <c r="Q214" s="274"/>
-      <c r="R214" s="274"/>
-      <c r="S214" s="274"/>
-      <c r="T214" s="274"/>
-      <c r="U214" s="274"/>
-      <c r="V214" s="274"/>
+      <c r="B214" s="252"/>
+      <c r="C214" s="252"/>
+      <c r="D214" s="252"/>
+      <c r="E214" s="252"/>
+      <c r="F214" s="252"/>
+      <c r="G214" s="252"/>
+      <c r="H214" s="252"/>
+      <c r="I214" s="252"/>
+      <c r="J214" s="252"/>
+      <c r="K214" s="252"/>
+      <c r="L214" s="252"/>
+      <c r="M214" s="252"/>
+      <c r="N214" s="252"/>
+      <c r="O214" s="252"/>
+      <c r="P214" s="252"/>
+      <c r="Q214" s="252"/>
+      <c r="R214" s="252"/>
+      <c r="S214" s="252"/>
+      <c r="T214" s="252"/>
+      <c r="U214" s="252"/>
+      <c r="V214" s="252"/>
       <c r="W214" s="71"/>
       <c r="X214" s="71"/>
     </row>
@@ -53393,20 +53404,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="TkRzYMMi7/nnAgu9wchrB6Ee0fH0e5xzmZs1qei8jXVcQ/fXmKTaNcRUmTglZSdCOKQPzOlTy0rGUvtbsDyYXQ==" saltValue="4SYFYy9cPxUnmQoIkzP7Vw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="40">
-    <mergeCell ref="P213:Q213"/>
-    <mergeCell ref="U213:V213"/>
-    <mergeCell ref="A214:V214"/>
-    <mergeCell ref="C195:I195"/>
-    <mergeCell ref="K195:X195"/>
-    <mergeCell ref="C202:I202"/>
-    <mergeCell ref="K202:X202"/>
-    <mergeCell ref="C209:I209"/>
-    <mergeCell ref="K209:X209"/>
-    <mergeCell ref="S110:S111"/>
-    <mergeCell ref="U110:U111"/>
-    <mergeCell ref="V110:V111"/>
-    <mergeCell ref="W110:W111"/>
-    <mergeCell ref="X110:X111"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="A6:V6"/>
+    <mergeCell ref="A212:X212"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="A57:V57"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="U96:V96"/>
     <mergeCell ref="A97:V97"/>
     <mergeCell ref="A110:A111"/>
     <mergeCell ref="C110:C111"/>
@@ -53423,16 +53430,20 @@
     <mergeCell ref="O110:O111"/>
     <mergeCell ref="P110:P111"/>
     <mergeCell ref="R110:R111"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="U56:V56"/>
-    <mergeCell ref="A57:V57"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="U96:V96"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="A6:V6"/>
-    <mergeCell ref="A212:X212"/>
+    <mergeCell ref="S110:S111"/>
+    <mergeCell ref="U110:U111"/>
+    <mergeCell ref="V110:V111"/>
+    <mergeCell ref="W110:W111"/>
+    <mergeCell ref="X110:X111"/>
+    <mergeCell ref="P213:Q213"/>
+    <mergeCell ref="U213:V213"/>
+    <mergeCell ref="A214:V214"/>
+    <mergeCell ref="C195:I195"/>
+    <mergeCell ref="K195:X195"/>
+    <mergeCell ref="C202:I202"/>
+    <mergeCell ref="K202:X202"/>
+    <mergeCell ref="C209:I209"/>
+    <mergeCell ref="K209:X209"/>
   </mergeCells>
   <conditionalFormatting sqref="C27">
     <cfRule type="dataBar" priority="1">
@@ -53568,15 +53579,15 @@
       <c r="O2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="268" t="s">
+      <c r="P2" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="269"/>
+      <c r="Q2" s="262"/>
       <c r="R2" s="8"/>
-      <c r="S2" s="270" t="s">
+      <c r="S2" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="271"/>
+      <c r="T2" s="260"/>
       <c r="U2" s="57" t="s">
         <v>152</v>
       </c>
@@ -53593,28 +53604,28 @@
       <c r="U3" s="70"/>
     </row>
     <row r="4" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="273" t="s">
+      <c r="A4" s="281" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="273"/>
-      <c r="C4" s="273"/>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
-      <c r="M4" s="273"/>
-      <c r="N4" s="273"/>
-      <c r="O4" s="273"/>
-      <c r="P4" s="273"/>
-      <c r="Q4" s="273"/>
-      <c r="R4" s="273"/>
-      <c r="S4" s="273"/>
-      <c r="T4" s="273"/>
+      <c r="B4" s="281"/>
+      <c r="C4" s="281"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="281"/>
+      <c r="I4" s="281"/>
+      <c r="J4" s="281"/>
+      <c r="K4" s="281"/>
+      <c r="L4" s="281"/>
+      <c r="M4" s="281"/>
+      <c r="N4" s="281"/>
+      <c r="O4" s="281"/>
+      <c r="P4" s="281"/>
+      <c r="Q4" s="281"/>
+      <c r="R4" s="281"/>
+      <c r="S4" s="281"/>
+      <c r="T4" s="281"/>
       <c r="U4" s="71"/>
     </row>
     <row r="5" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -54414,42 +54425,42 @@
       <c r="O18" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="P18" s="275" t="s">
+      <c r="P18" s="253" t="s">
         <v>6</v>
       </c>
-      <c r="Q18" s="276"/>
+      <c r="Q18" s="254"/>
       <c r="R18" s="53"/>
-      <c r="S18" s="277" t="s">
+      <c r="S18" s="255" t="s">
         <v>7</v>
       </c>
-      <c r="T18" s="278"/>
+      <c r="T18" s="256"/>
       <c r="U18" s="58" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="272" t="s">
+      <c r="A19" s="280" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="272"/>
-      <c r="C19" s="272"/>
-      <c r="D19" s="272"/>
-      <c r="E19" s="272"/>
-      <c r="F19" s="272"/>
-      <c r="G19" s="272"/>
-      <c r="H19" s="272"/>
-      <c r="I19" s="272"/>
-      <c r="J19" s="272"/>
-      <c r="K19" s="272"/>
-      <c r="L19" s="272"/>
-      <c r="M19" s="272"/>
-      <c r="N19" s="272"/>
-      <c r="O19" s="272"/>
-      <c r="P19" s="272"/>
-      <c r="Q19" s="272"/>
-      <c r="R19" s="272"/>
-      <c r="S19" s="272"/>
-      <c r="T19" s="272"/>
+      <c r="B19" s="280"/>
+      <c r="C19" s="280"/>
+      <c r="D19" s="280"/>
+      <c r="E19" s="280"/>
+      <c r="F19" s="280"/>
+      <c r="G19" s="280"/>
+      <c r="H19" s="280"/>
+      <c r="I19" s="280"/>
+      <c r="J19" s="280"/>
+      <c r="K19" s="280"/>
+      <c r="L19" s="280"/>
+      <c r="M19" s="280"/>
+      <c r="N19" s="280"/>
+      <c r="O19" s="280"/>
+      <c r="P19" s="280"/>
+      <c r="Q19" s="280"/>
+      <c r="R19" s="280"/>
+      <c r="S19" s="280"/>
+      <c r="T19" s="280"/>
       <c r="U19" s="71"/>
     </row>
     <row r="20" spans="1:21" s="90" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -55522,42 +55533,42 @@
       <c r="O37" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="P37" s="279" t="s">
+      <c r="P37" s="257" t="s">
         <v>6</v>
       </c>
-      <c r="Q37" s="280"/>
+      <c r="Q37" s="258"/>
       <c r="R37" s="56"/>
-      <c r="S37" s="270" t="s">
+      <c r="S37" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="T37" s="271"/>
+      <c r="T37" s="260"/>
       <c r="U37" s="59" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="274" t="s">
+      <c r="A38" s="252" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="274"/>
-      <c r="C38" s="274"/>
-      <c r="D38" s="274"/>
-      <c r="E38" s="274"/>
-      <c r="F38" s="274"/>
-      <c r="G38" s="274"/>
-      <c r="H38" s="274"/>
-      <c r="I38" s="274"/>
-      <c r="J38" s="274"/>
-      <c r="K38" s="274"/>
-      <c r="L38" s="274"/>
-      <c r="M38" s="274"/>
-      <c r="N38" s="274"/>
-      <c r="O38" s="274"/>
-      <c r="P38" s="274"/>
-      <c r="Q38" s="274"/>
-      <c r="R38" s="274"/>
-      <c r="S38" s="274"/>
-      <c r="T38" s="274"/>
+      <c r="B38" s="252"/>
+      <c r="C38" s="252"/>
+      <c r="D38" s="252"/>
+      <c r="E38" s="252"/>
+      <c r="F38" s="252"/>
+      <c r="G38" s="252"/>
+      <c r="H38" s="252"/>
+      <c r="I38" s="252"/>
+      <c r="J38" s="252"/>
+      <c r="K38" s="252"/>
+      <c r="L38" s="252"/>
+      <c r="M38" s="252"/>
+      <c r="N38" s="252"/>
+      <c r="O38" s="252"/>
+      <c r="P38" s="252"/>
+      <c r="Q38" s="252"/>
+      <c r="R38" s="252"/>
+      <c r="S38" s="252"/>
+      <c r="T38" s="252"/>
       <c r="U38" s="71"/>
     </row>
     <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57564,42 +57575,42 @@
       <c r="O71" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="P71" s="268" t="s">
+      <c r="P71" s="261" t="s">
         <v>6</v>
       </c>
-      <c r="Q71" s="269"/>
+      <c r="Q71" s="262"/>
       <c r="R71" s="8"/>
-      <c r="S71" s="270" t="s">
+      <c r="S71" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="T71" s="271"/>
+      <c r="T71" s="260"/>
       <c r="U71" s="57" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="281" t="s">
+      <c r="A72" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="281"/>
-      <c r="C72" s="281"/>
-      <c r="D72" s="281"/>
-      <c r="E72" s="281"/>
-      <c r="F72" s="281"/>
-      <c r="G72" s="281"/>
-      <c r="H72" s="281"/>
-      <c r="I72" s="281"/>
-      <c r="J72" s="281"/>
-      <c r="K72" s="281"/>
-      <c r="L72" s="281"/>
-      <c r="M72" s="281"/>
-      <c r="N72" s="281"/>
-      <c r="O72" s="281"/>
-      <c r="P72" s="281"/>
-      <c r="Q72" s="281"/>
-      <c r="R72" s="281"/>
-      <c r="S72" s="281"/>
-      <c r="T72" s="281"/>
+      <c r="B72" s="263"/>
+      <c r="C72" s="263"/>
+      <c r="D72" s="263"/>
+      <c r="E72" s="263"/>
+      <c r="F72" s="263"/>
+      <c r="G72" s="263"/>
+      <c r="H72" s="263"/>
+      <c r="I72" s="263"/>
+      <c r="J72" s="263"/>
+      <c r="K72" s="263"/>
+      <c r="L72" s="263"/>
+      <c r="M72" s="263"/>
+      <c r="N72" s="263"/>
+      <c r="O72" s="263"/>
+      <c r="P72" s="263"/>
+      <c r="Q72" s="263"/>
+      <c r="R72" s="263"/>
+      <c r="S72" s="263"/>
+      <c r="T72" s="263"/>
       <c r="U72" s="71"/>
     </row>
     <row r="73" spans="1:22" s="180" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
